--- a/artfynd/A 27434-2025 artfynd.xlsx
+++ b/artfynd/A 27434-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114569849</v>
+        <v>110392938</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Horndal-Fallviken, Gstr</t>
+          <t>Gästrikeleden, Gästrikeleden, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573902</v>
+        <v>574155</v>
       </c>
       <c r="R2" t="n">
-        <v>6703674</v>
+        <v>6703598</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,12 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>21:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>21:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,22 +765,330 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>fanny westling</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>fanny westling</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113680439</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93263</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>vreten, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>574162</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6703584</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114571368</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Horndal-Fallviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>573890</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6703398</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Mårten Nilsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Ward Tamsyn</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114569849</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Horndal-Fallviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>573902</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6703674</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27434-2025 artfynd.xlsx
+++ b/artfynd/A 27434-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110392938</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680439</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114571368</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,8 +1109,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114569849</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>